--- a/input/images/tables/assessments-valuesets.xlsx
+++ b/input/images/tables/assessments-valuesets.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2892,6 +2892,62 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>8</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Nutrition Assessment</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>nutrition-assessment</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>US Core Nutrition Assessment</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ValueSet-us-core-nutrition-assessment.html</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Placeholder set of the LOINC Nutrition assessment panel (75282-4) panel items pending a terminology decision</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
